--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260703.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>9.89%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>25,098,000</t>
+          <t>4,486,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>9.22%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>4,486,000</t>
+          <t>25,098,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.60%</t>
+          <t>8.87%</t>
         </is>
       </c>
     </row>
@@ -682,46 +682,46 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>7.14%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,334,000</t>
+          <t>2,382,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.94%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,382,000</t>
+          <t>6,334,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -733,44 +733,44 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>15,203,000</t>
+          <t>86,550,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>4.99%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>86,550,000</t>
+          <t>15,203,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>4.98%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.84%</t>
         </is>
       </c>
     </row>
@@ -814,73 +814,73 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.30%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>5,614,000</t>
+          <t>8,315,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.67%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,315,000</t>
+          <t>8,949,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>8,949,000</t>
+          <t>5,052,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12,742,000</t>
+          <t>5,160,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,160,000</t>
+          <t>12,742,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>252,000</t>
+          <t>226,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>457,000</t>
+          <t>411,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,808,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>3,427,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1232,112 +1232,112 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>291,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,508,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,56 +1349,56 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>10,128,869,928</t>
+          <t>12,552,541,768</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,875,967,632</t>
+          <t>3,766,455,179</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
